--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H670"/>
+  <dimension ref="A1:H672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20538,6 +20538,66 @@
         <v>352.43</v>
       </c>
       <c r="H670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>335.43</v>
+      </c>
+      <c r="C671" t="n">
+        <v>346.02</v>
+      </c>
+      <c r="D671" t="n">
+        <v>356.36</v>
+      </c>
+      <c r="E671" t="n">
+        <v>362.76</v>
+      </c>
+      <c r="F671" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="G671" t="n">
+        <v>347.73</v>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>335.09</v>
+      </c>
+      <c r="C672" t="n">
+        <v>345.01</v>
+      </c>
+      <c r="D672" t="n">
+        <v>355.96</v>
+      </c>
+      <c r="E672" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="F672" t="n">
+        <v>356.44</v>
+      </c>
+      <c r="G672" t="n">
+        <v>347.51</v>
+      </c>
+      <c r="H672" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20554,7 +20614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B713"/>
+  <dimension ref="A1:B715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27687,6 +27747,26 @@
       </c>
       <c r="B713" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -27855,28 +27935,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3171194113939367</v>
+        <v>0.3108759521646185</v>
       </c>
       <c r="J2" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K2" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06156249565374006</v>
+        <v>0.05942749036831974</v>
       </c>
       <c r="M2" t="n">
-        <v>7.498496772216003</v>
+        <v>7.50413829081718</v>
       </c>
       <c r="N2" t="n">
-        <v>82.0885484357421</v>
+        <v>82.17719242986017</v>
       </c>
       <c r="O2" t="n">
-        <v>9.060273088364506</v>
+        <v>9.065163673638782</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5026478711582</v>
+        <v>337.5698400700677</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27933,28 +28013,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2009293745846662</v>
+        <v>0.1960919206099246</v>
       </c>
       <c r="J3" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K3" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02945598286219953</v>
+        <v>0.02818822069053428</v>
       </c>
       <c r="M3" t="n">
-        <v>6.993803074458746</v>
+        <v>6.991651844672313</v>
       </c>
       <c r="N3" t="n">
-        <v>71.23220155751713</v>
+        <v>71.22066884521847</v>
       </c>
       <c r="O3" t="n">
-        <v>8.439917153474738</v>
+        <v>8.439233901558747</v>
       </c>
       <c r="P3" t="n">
-        <v>348.4333448049883</v>
+        <v>348.4854068312813</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28011,28 +28091,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03266869773986524</v>
+        <v>0.02937369031542254</v>
       </c>
       <c r="J4" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K4" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008818446738694252</v>
+        <v>0.000716495434247344</v>
       </c>
       <c r="M4" t="n">
-        <v>6.651216621636684</v>
+        <v>6.647172694636885</v>
       </c>
       <c r="N4" t="n">
-        <v>64.74946494012001</v>
+        <v>64.64939521509174</v>
       </c>
       <c r="O4" t="n">
-        <v>8.046705222643613</v>
+        <v>8.040484762443851</v>
       </c>
       <c r="P4" t="n">
-        <v>360.8997050111325</v>
+        <v>360.9351662909521</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28089,28 +28169,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0779778773344786</v>
+        <v>-0.07970885888686048</v>
       </c>
       <c r="J5" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K5" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006673494285504344</v>
+        <v>0.007010768337808893</v>
       </c>
       <c r="M5" t="n">
-        <v>5.723217979381529</v>
+        <v>5.715829960641106</v>
       </c>
       <c r="N5" t="n">
-        <v>48.46512455154088</v>
+        <v>48.34641297926638</v>
       </c>
       <c r="O5" t="n">
-        <v>6.961689777025466</v>
+        <v>6.953158489439629</v>
       </c>
       <c r="P5" t="n">
-        <v>367.9668331008634</v>
+        <v>367.9854610660469</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28167,28 +28247,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.005518398016919194</v>
+        <v>-0.008161430140914784</v>
       </c>
       <c r="J6" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K6" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L6" t="n">
-        <v>3.076528975110016e-05</v>
+        <v>6.763599266645937e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>5.889923143302949</v>
+        <v>5.887592636892046</v>
       </c>
       <c r="N6" t="n">
-        <v>53.00287835043585</v>
+        <v>52.90508828613179</v>
       </c>
       <c r="O6" t="n">
-        <v>7.28030757251614</v>
+        <v>7.273588405053711</v>
       </c>
       <c r="P6" t="n">
-        <v>361.4876423011701</v>
+        <v>361.5160877897439</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28245,28 +28325,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06179353528757117</v>
+        <v>0.05976827360848187</v>
       </c>
       <c r="J7" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K7" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003906790609301103</v>
+        <v>0.00367623782750981</v>
       </c>
       <c r="M7" t="n">
-        <v>5.773713466419838</v>
+        <v>5.767043015108369</v>
       </c>
       <c r="N7" t="n">
-        <v>52.13311956731861</v>
+        <v>52.01282751536206</v>
       </c>
       <c r="O7" t="n">
-        <v>7.22032683244454</v>
+        <v>7.211991924244097</v>
       </c>
       <c r="P7" t="n">
-        <v>349.4326329222825</v>
+        <v>349.4544289961799</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28304,7 +28384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H670"/>
+  <dimension ref="A1:H672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56447,6 +56527,90 @@
         </is>
       </c>
     </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-37.18107153087298,175.88502253382825</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-37.181767761314504,175.88525318088895</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-37.18246601712176,175.88548083348792</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-37.18314048590966,175.88576728434947</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>-37.18382701086811,175.88602692301424</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-37.184519644877234,175.8862871596269</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-37.18107197474737,175.88501874698585</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-37.18176907990354,175.88524193164136</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-37.182466753036636,175.88547642568463</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-37.18313930959821,175.8857716592818</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>-37.18382988695648,175.8860185432491</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-37.184520468722944,175.8862849072545</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H672"/>
+  <dimension ref="A1:H675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20598,6 +20598,96 @@
         <v>347.51</v>
       </c>
       <c r="H672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="C673" t="n">
+        <v>344.05</v>
+      </c>
+      <c r="D673" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="E673" t="n">
+        <v>363.11</v>
+      </c>
+      <c r="F673" t="n">
+        <v>356.49</v>
+      </c>
+      <c r="G673" t="n">
+        <v>347.47</v>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="C674" t="n">
+        <v>343.89</v>
+      </c>
+      <c r="D674" t="n">
+        <v>357.09</v>
+      </c>
+      <c r="E674" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="F674" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="G674" t="n">
+        <v>348.12</v>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>334.21</v>
+      </c>
+      <c r="C675" t="n">
+        <v>344.67</v>
+      </c>
+      <c r="D675" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="E675" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="F675" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="G675" t="n">
+        <v>349.06</v>
+      </c>
+      <c r="H675" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20614,7 +20704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B715"/>
+  <dimension ref="A1:B718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27767,6 +27857,36 @@
       </c>
       <c r="B715" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -27935,28 +28055,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3108759521646185</v>
+        <v>0.3006449479222403</v>
       </c>
       <c r="J2" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K2" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05942749036831974</v>
+        <v>0.05590049436085132</v>
       </c>
       <c r="M2" t="n">
-        <v>7.50413829081718</v>
+        <v>7.516873372788457</v>
       </c>
       <c r="N2" t="n">
-        <v>82.17719242986017</v>
+        <v>82.41391473107521</v>
       </c>
       <c r="O2" t="n">
-        <v>9.065163673638782</v>
+        <v>9.07821098736283</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5698400700677</v>
+        <v>337.6801793529809</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28013,28 +28133,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1960919206099246</v>
+        <v>0.1878169930903863</v>
       </c>
       <c r="J3" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K3" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02818822069053428</v>
+        <v>0.026015603604578</v>
       </c>
       <c r="M3" t="n">
-        <v>6.991651844672313</v>
+        <v>6.992186382580603</v>
       </c>
       <c r="N3" t="n">
-        <v>71.22066884521847</v>
+        <v>71.29818281470828</v>
       </c>
       <c r="O3" t="n">
-        <v>8.439233901558747</v>
+        <v>8.443825129330207</v>
       </c>
       <c r="P3" t="n">
-        <v>348.4854068312813</v>
+        <v>348.5746492540637</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28091,28 +28211,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02937369031542254</v>
+        <v>0.02539680208073605</v>
       </c>
       <c r="J4" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K4" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000716495434247344</v>
+        <v>0.0005399600770786828</v>
       </c>
       <c r="M4" t="n">
-        <v>6.647172694636885</v>
+        <v>6.63655035780755</v>
       </c>
       <c r="N4" t="n">
-        <v>64.64939521509174</v>
+        <v>64.45438295262376</v>
       </c>
       <c r="O4" t="n">
-        <v>8.040484762443851</v>
+        <v>8.028348706466589</v>
       </c>
       <c r="P4" t="n">
-        <v>360.9351662909521</v>
+        <v>360.978053775996</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28169,28 +28289,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07970885888686048</v>
+        <v>-0.08131926457280556</v>
       </c>
       <c r="J5" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K5" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007010768337808893</v>
+        <v>0.007360102114557621</v>
       </c>
       <c r="M5" t="n">
-        <v>5.715829960641106</v>
+        <v>5.699314271973249</v>
       </c>
       <c r="N5" t="n">
-        <v>48.34641297926638</v>
+        <v>48.14878958068157</v>
       </c>
       <c r="O5" t="n">
-        <v>6.953158489439629</v>
+        <v>6.938932884866488</v>
       </c>
       <c r="P5" t="n">
-        <v>367.9854610660469</v>
+        <v>368.0028260488535</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28247,28 +28367,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.008161430140914784</v>
+        <v>-0.01178127175735082</v>
       </c>
       <c r="J6" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K6" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L6" t="n">
-        <v>6.763599266645937e-05</v>
+        <v>0.00014204159030895</v>
       </c>
       <c r="M6" t="n">
-        <v>5.887592636892046</v>
+        <v>5.882113520202666</v>
       </c>
       <c r="N6" t="n">
-        <v>52.90508828613179</v>
+        <v>52.74699602619643</v>
       </c>
       <c r="O6" t="n">
-        <v>7.273588405053711</v>
+        <v>7.262712718137516</v>
       </c>
       <c r="P6" t="n">
-        <v>361.5160877897439</v>
+        <v>361.5551247374286</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28325,28 +28445,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05976827360848187</v>
+        <v>0.05730592042159137</v>
       </c>
       <c r="J7" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="K7" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00367623782750981</v>
+        <v>0.003409767228200855</v>
       </c>
       <c r="M7" t="n">
-        <v>5.767043015108369</v>
+        <v>5.754148584779637</v>
       </c>
       <c r="N7" t="n">
-        <v>52.01282751536206</v>
+        <v>51.81809950350956</v>
       </c>
       <c r="O7" t="n">
-        <v>7.211991924244097</v>
+        <v>7.198478971526524</v>
       </c>
       <c r="P7" t="n">
-        <v>349.4544289961799</v>
+        <v>349.4809825350663</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28384,7 +28504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H672"/>
+  <dimension ref="A1:H675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56611,6 +56731,132 @@
         </is>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-37.18107303221233,175.88500972539057</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-37.18177033321492,175.8852312392868</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-37.182465888336644,175.8854816048535</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-37.18313948174136,175.88577101904784</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-37.18382970942017,175.88601906051855</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-37.184520618513076,175.88628449773222</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-37.18107368496814,175.88500415650446</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-37.18177054210006,175.88522945722767</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-37.18246467407671,175.8854888777287</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-37.18313695697484,175.88578040914607</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-37.18382821811516,175.88602340558205</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-37.18451818442337,175.88629115246877</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-37.18107312359817,175.8850089457465</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-37.18176952378476,175.88523814476585</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-37.18246309185859,175.88549835450513</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-37.183134087921104,175.88579107971142</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-37.1838240992719,175.88603540623257</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-37.18451466435457,175.8863007762409</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H675"/>
+  <dimension ref="A1:H677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20688,6 +20688,66 @@
         <v>349.06</v>
       </c>
       <c r="H675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>335.36</v>
+      </c>
+      <c r="C676" t="n">
+        <v>346.69</v>
+      </c>
+      <c r="D676" t="n">
+        <v>362.16</v>
+      </c>
+      <c r="E676" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="F676" t="n">
+        <v>361.57</v>
+      </c>
+      <c r="G676" t="n">
+        <v>354</v>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>335.37</v>
+      </c>
+      <c r="C677" t="n">
+        <v>346.45</v>
+      </c>
+      <c r="D677" t="n">
+        <v>362.32</v>
+      </c>
+      <c r="E677" t="n">
+        <v>367.75</v>
+      </c>
+      <c r="F677" t="n">
+        <v>360.52</v>
+      </c>
+      <c r="G677" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="H677" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20704,7 +20764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B718"/>
+  <dimension ref="A1:B720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27887,6 +27947,26 @@
       </c>
       <c r="B718" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -28055,28 +28135,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3006449479222403</v>
+        <v>0.2946001115627386</v>
       </c>
       <c r="J2" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="K2" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05590049436085132</v>
+        <v>0.05392359773342181</v>
       </c>
       <c r="M2" t="n">
-        <v>7.516873372788457</v>
+        <v>7.521854024319944</v>
       </c>
       <c r="N2" t="n">
-        <v>82.41391473107521</v>
+        <v>82.48235689350908</v>
       </c>
       <c r="O2" t="n">
-        <v>9.07821098736283</v>
+        <v>9.081979789314062</v>
       </c>
       <c r="P2" t="n">
-        <v>337.6801793529809</v>
+        <v>337.7458301478025</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28133,28 +28213,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1878169930903863</v>
+        <v>0.1837135946608988</v>
       </c>
       <c r="J3" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="K3" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L3" t="n">
-        <v>0.026015603604578</v>
+        <v>0.02502386461324058</v>
       </c>
       <c r="M3" t="n">
-        <v>6.992186382580603</v>
+        <v>6.986843993114571</v>
       </c>
       <c r="N3" t="n">
-        <v>71.29818281470828</v>
+        <v>71.23117233263569</v>
       </c>
       <c r="O3" t="n">
-        <v>8.443825129330207</v>
+        <v>8.439856179617973</v>
       </c>
       <c r="P3" t="n">
-        <v>348.5746492540637</v>
+        <v>348.6192155727412</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28211,28 +28291,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02539680208073605</v>
+        <v>0.02573953619813811</v>
       </c>
       <c r="J4" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="K4" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005399600770786828</v>
+        <v>0.0005581286518018258</v>
       </c>
       <c r="M4" t="n">
-        <v>6.63655035780755</v>
+        <v>6.618742862865775</v>
       </c>
       <c r="N4" t="n">
-        <v>64.45438295262376</v>
+        <v>64.26471040618435</v>
       </c>
       <c r="O4" t="n">
-        <v>8.028348706466589</v>
+        <v>8.016527328350122</v>
       </c>
       <c r="P4" t="n">
-        <v>360.978053775996</v>
+        <v>360.9743309699277</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28289,28 +28369,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08131926457280556</v>
+        <v>-0.08016668618592206</v>
       </c>
       <c r="J5" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="K5" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007360102114557621</v>
+        <v>0.007197756354066054</v>
       </c>
       <c r="M5" t="n">
-        <v>5.699314271973249</v>
+        <v>5.687714336652482</v>
       </c>
       <c r="N5" t="n">
-        <v>48.14878958068157</v>
+        <v>48.01770179826696</v>
       </c>
       <c r="O5" t="n">
-        <v>6.938932884866488</v>
+        <v>6.929480629763457</v>
       </c>
       <c r="P5" t="n">
-        <v>368.0028260488535</v>
+        <v>367.9903086866889</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28367,28 +28447,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01178127175735082</v>
+        <v>-0.01189561742203753</v>
       </c>
       <c r="J6" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="K6" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00014204159030895</v>
+        <v>0.0001457270050708726</v>
       </c>
       <c r="M6" t="n">
-        <v>5.882113520202666</v>
+        <v>5.86633352390314</v>
       </c>
       <c r="N6" t="n">
-        <v>52.74699602619643</v>
+        <v>52.59186141881742</v>
       </c>
       <c r="O6" t="n">
-        <v>7.262712718137516</v>
+        <v>7.252024642733739</v>
       </c>
       <c r="P6" t="n">
-        <v>361.5551247374286</v>
+        <v>361.5563699662925</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28445,28 +28525,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05730592042159137</v>
+        <v>0.05864677514122611</v>
       </c>
       <c r="J7" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="K7" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003409767228200855</v>
+        <v>0.003592007310417755</v>
       </c>
       <c r="M7" t="n">
-        <v>5.754148584779637</v>
+        <v>5.743722209333801</v>
       </c>
       <c r="N7" t="n">
-        <v>51.81809950350956</v>
+        <v>51.68162511404866</v>
       </c>
       <c r="O7" t="n">
-        <v>7.198478971526524</v>
+        <v>7.188993331061635</v>
       </c>
       <c r="P7" t="n">
-        <v>349.4809825350663</v>
+        <v>349.4664244914781</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28504,7 +28584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H675"/>
+  <dimension ref="A1:H677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56857,6 +56937,90 @@
         </is>
       </c>
     </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-37.1810716222589,175.88502175418424</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-37.18176688660635,175.88526064326086</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-37.18245534633814,175.88554474662502</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-37.18312585373171,175.8858217042292</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>-37.183811671720576,175.8860716150837</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-37.18449616525731,175.88635135221926</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-37.18107160920377,175.88502186556195</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-37.18176719993471,175.88525797017243</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-37.18245505197122,175.88554650974578</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-37.18312616932795,175.88582053046733</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>-37.18381539998709,175.88606075242967</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-37.18450140791854,175.88633701894867</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H677"/>
+  <dimension ref="A1:H678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20748,6 +20748,36 @@
         <v>352.6</v>
       </c>
       <c r="H677" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>337.37</v>
+      </c>
+      <c r="C678" t="n">
+        <v>346.85</v>
+      </c>
+      <c r="D678" t="n">
+        <v>363.24</v>
+      </c>
+      <c r="E678" t="n">
+        <v>369.15</v>
+      </c>
+      <c r="F678" t="n">
+        <v>362.89</v>
+      </c>
+      <c r="G678" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="H678" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20764,7 +20794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27967,6 +27997,26 @@
       </c>
       <c r="B720" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -28135,28 +28185,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2946001115627386</v>
+        <v>0.2921688001013293</v>
       </c>
       <c r="J2" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K2" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05392359773342181</v>
+        <v>0.05318384847917834</v>
       </c>
       <c r="M2" t="n">
-        <v>7.521854024319944</v>
+        <v>7.521552071775749</v>
       </c>
       <c r="N2" t="n">
-        <v>82.48235689350908</v>
+        <v>82.46074221941436</v>
       </c>
       <c r="O2" t="n">
-        <v>9.081979789314062</v>
+        <v>9.080789735447812</v>
       </c>
       <c r="P2" t="n">
-        <v>337.7458301478025</v>
+        <v>337.772361447479</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28213,28 +28263,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1837135946608988</v>
+        <v>0.181746627464454</v>
       </c>
       <c r="J3" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K3" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02502386461324058</v>
+        <v>0.02455835246211047</v>
       </c>
       <c r="M3" t="n">
-        <v>6.986843993114571</v>
+        <v>6.983769177407781</v>
       </c>
       <c r="N3" t="n">
-        <v>71.23117233263569</v>
+        <v>71.19155119572184</v>
       </c>
       <c r="O3" t="n">
-        <v>8.439856179617973</v>
+        <v>8.437508589371737</v>
       </c>
       <c r="P3" t="n">
-        <v>348.6192155727412</v>
+        <v>348.64067978947</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28291,28 +28341,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02573953619813811</v>
+        <v>0.0262045874477623</v>
       </c>
       <c r="J4" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K4" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005581286518018258</v>
+        <v>0.0005802843219518961</v>
       </c>
       <c r="M4" t="n">
-        <v>6.618742862865775</v>
+        <v>6.611419095953896</v>
       </c>
       <c r="N4" t="n">
-        <v>64.26471040618435</v>
+        <v>64.17345139986803</v>
       </c>
       <c r="O4" t="n">
-        <v>8.016527328350122</v>
+        <v>8.010833377362685</v>
       </c>
       <c r="P4" t="n">
-        <v>360.9743309699277</v>
+        <v>360.9692561721223</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28369,28 +28419,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08016668618592206</v>
+        <v>-0.07919312416511276</v>
       </c>
       <c r="J5" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K5" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007197756354066054</v>
+        <v>0.007045197513464885</v>
       </c>
       <c r="M5" t="n">
-        <v>5.687714336652482</v>
+        <v>5.683703053292195</v>
       </c>
       <c r="N5" t="n">
-        <v>48.01770179826696</v>
+        <v>47.96284411299892</v>
       </c>
       <c r="O5" t="n">
-        <v>6.929480629763457</v>
+        <v>6.92552121598071</v>
       </c>
       <c r="P5" t="n">
-        <v>367.9903086866889</v>
+        <v>367.9796848459602</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28447,28 +28497,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01189561742203753</v>
+        <v>-0.01140809652265702</v>
       </c>
       <c r="J6" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K6" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001457270050708726</v>
+        <v>0.0001344471979518591</v>
       </c>
       <c r="M6" t="n">
-        <v>5.86633352390314</v>
+        <v>5.859789761163866</v>
       </c>
       <c r="N6" t="n">
-        <v>52.59186141881742</v>
+        <v>52.51820731978754</v>
       </c>
       <c r="O6" t="n">
-        <v>7.252024642733739</v>
+        <v>7.246944688611024</v>
       </c>
       <c r="P6" t="n">
-        <v>361.5563699662925</v>
+        <v>361.5510499720074</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28525,28 +28575,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05864677514122611</v>
+        <v>0.05985634626955823</v>
       </c>
       <c r="J7" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K7" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003592007310417755</v>
+        <v>0.003751275527273723</v>
       </c>
       <c r="M7" t="n">
-        <v>5.743722209333801</v>
+        <v>5.741117737679114</v>
       </c>
       <c r="N7" t="n">
-        <v>51.68162511404866</v>
+        <v>51.63009085397558</v>
       </c>
       <c r="O7" t="n">
-        <v>7.188993331061635</v>
+        <v>7.185408189795176</v>
       </c>
       <c r="P7" t="n">
-        <v>349.4664244914781</v>
+        <v>349.4532252388956</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28584,7 +28634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H677"/>
+  <dimension ref="A1:H678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57021,6 +57071,48 @@
         </is>
       </c>
     </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-37.181068998175675,175.88504414110437</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-37.181766677720745,175.88526242531978</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-37.182453359360906,175.8855566476897</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-37.183122152647556,175.88583546925403</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>-37.183806984755606,175.88608527098998</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>-37.18449189623193,175.88636302359524</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H678"/>
+  <dimension ref="A1:H682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20778,6 +20778,126 @@
         <v>355.14</v>
       </c>
       <c r="H678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>338.17</v>
+      </c>
+      <c r="C679" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="D679" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="E679" t="n">
+        <v>368.77</v>
+      </c>
+      <c r="F679" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="G679" t="n">
+        <v>355.16</v>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>337.85</v>
+      </c>
+      <c r="C680" t="n">
+        <v>346.87</v>
+      </c>
+      <c r="D680" t="n">
+        <v>362.88</v>
+      </c>
+      <c r="E680" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="F680" t="n">
+        <v>363.04</v>
+      </c>
+      <c r="G680" t="n">
+        <v>354.85</v>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>337.13</v>
+      </c>
+      <c r="C681" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="D681" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="E681" t="n">
+        <v>367.32</v>
+      </c>
+      <c r="F681" t="n">
+        <v>362.61</v>
+      </c>
+      <c r="G681" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>336.08</v>
+      </c>
+      <c r="C682" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="D682" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="E682" t="n">
+        <v>369.23</v>
+      </c>
+      <c r="F682" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="G682" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="H682" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20794,7 +20914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28017,6 +28137,46 @@
       </c>
       <c r="B722" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
@@ -28185,28 +28345,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2921688001013293</v>
+        <v>0.2825000637103376</v>
       </c>
       <c r="J2" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K2" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05318384847917834</v>
+        <v>0.05026962546094071</v>
       </c>
       <c r="M2" t="n">
-        <v>7.521552071775749</v>
+        <v>7.520268769921071</v>
       </c>
       <c r="N2" t="n">
-        <v>82.46074221941436</v>
+        <v>82.37772540516973</v>
       </c>
       <c r="O2" t="n">
-        <v>9.080789735447812</v>
+        <v>9.076217571498038</v>
       </c>
       <c r="P2" t="n">
-        <v>337.772361447479</v>
+        <v>337.878216464661</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28263,28 +28423,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.181746627464454</v>
+        <v>0.173869785751493</v>
       </c>
       <c r="J3" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K3" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02455835246211047</v>
+        <v>0.02272236765583546</v>
       </c>
       <c r="M3" t="n">
-        <v>6.983769177407781</v>
+        <v>6.971489958229283</v>
       </c>
       <c r="N3" t="n">
-        <v>71.19155119572184</v>
+        <v>71.03798460089619</v>
       </c>
       <c r="O3" t="n">
-        <v>8.437508589371737</v>
+        <v>8.428403443173339</v>
       </c>
       <c r="P3" t="n">
-        <v>348.64067978947</v>
+        <v>348.726913422631</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28341,28 +28501,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0262045874477623</v>
+        <v>0.02785697433438552</v>
       </c>
       <c r="J4" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K4" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005802843219518961</v>
+        <v>0.0006639913862550584</v>
       </c>
       <c r="M4" t="n">
-        <v>6.611419095953896</v>
+        <v>6.581193808422938</v>
       </c>
       <c r="N4" t="n">
-        <v>64.17345139986803</v>
+        <v>63.81091859462417</v>
       </c>
       <c r="O4" t="n">
-        <v>8.010833377362685</v>
+        <v>7.988173670785092</v>
       </c>
       <c r="P4" t="n">
-        <v>360.9692561721223</v>
+        <v>360.9511676823444</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28419,28 +28579,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07919312416511276</v>
+        <v>-0.0762948042989868</v>
       </c>
       <c r="J5" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K5" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007045197513464885</v>
+        <v>0.006620383807362962</v>
       </c>
       <c r="M5" t="n">
-        <v>5.683703053292195</v>
+        <v>5.663234680655915</v>
       </c>
       <c r="N5" t="n">
-        <v>47.96284411299892</v>
+        <v>47.71995446778206</v>
       </c>
       <c r="O5" t="n">
-        <v>6.92552121598071</v>
+        <v>6.90796312003633</v>
       </c>
       <c r="P5" t="n">
-        <v>367.9796848459602</v>
+        <v>367.9479582400522</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28497,28 +28657,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01140809652265702</v>
+        <v>-0.009460137592964862</v>
       </c>
       <c r="J6" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K6" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001344471979518591</v>
+        <v>9.361449608158434e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>5.859789761163866</v>
+        <v>5.833767109952591</v>
       </c>
       <c r="N6" t="n">
-        <v>52.51820731978754</v>
+        <v>52.22628826653968</v>
       </c>
       <c r="O6" t="n">
-        <v>7.246944688611024</v>
+        <v>7.226775786375255</v>
       </c>
       <c r="P6" t="n">
-        <v>361.5510499720074</v>
+        <v>361.5297293998523</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28575,28 +28735,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05985634626955823</v>
+        <v>0.06444167299629971</v>
       </c>
       <c r="J7" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K7" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003751275527273723</v>
+        <v>0.00439336472844809</v>
       </c>
       <c r="M7" t="n">
-        <v>5.741117737679114</v>
+        <v>5.729606067629828</v>
       </c>
       <c r="N7" t="n">
-        <v>51.63009085397558</v>
+        <v>51.41645786805796</v>
       </c>
       <c r="O7" t="n">
-        <v>7.185408189795176</v>
+        <v>7.17052702861219</v>
       </c>
       <c r="P7" t="n">
-        <v>349.4532252388956</v>
+        <v>349.4030305125661</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28634,7 +28794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H678"/>
+  <dimension ref="A1:H682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57113,6 +57273,174 @@
         </is>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-37.18106795376329,175.88505305132082</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-37.18176615550664,175.88526688046707</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-37.182453101789704,175.88555819042023</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>-37.18312324288956,175.88583141444067</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>-37.18380556446289,175.88608940914307</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>-37.184491821336735,175.8863632283562</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-37.181068371528326,175.88504948723428</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-37.18176665161005,175.88526264807714</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-37.18245402168677,175.8855526806682</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>-37.18312527992032,175.88582383834168</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>-37.18380645214585,175.88608682279744</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>-37.18449298221218,175.88636005456112</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-37.18106931149927,175.88504146803936</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-37.181767004104486,175.8852596408527</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-37.18245543832779,175.88554419564977</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>-37.18312740302228,175.88581594212536</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>-37.18380797896043,175.88608237428275</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>-37.18449316945014,175.88635954265868</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>-37.181070682289274,175.88502977337973</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>-37.181767408820235,175.88525618811346</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>-37.18245197951492,175.88556491231753</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>-37.18312192312292,175.88583632289894</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>-37.18380748185802,175.88608382263638</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>-37.18449170899395,175.88636353549765</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H682"/>
+  <dimension ref="A1:H686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20898,6 +20898,126 @@
         <v>355.19</v>
       </c>
       <c r="H682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>334.82</v>
+      </c>
+      <c r="C683" t="n">
+        <v>345.16</v>
+      </c>
+      <c r="D683" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="E683" t="n">
+        <v>366.57</v>
+      </c>
+      <c r="F683" t="n">
+        <v>360.65</v>
+      </c>
+      <c r="G683" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>334.61</v>
+      </c>
+      <c r="C684" t="n">
+        <v>345.95</v>
+      </c>
+      <c r="D684" t="n">
+        <v>361.49</v>
+      </c>
+      <c r="E684" t="n">
+        <v>366.85</v>
+      </c>
+      <c r="F684" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="G684" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>334.61</v>
+      </c>
+      <c r="C685" t="n">
+        <v>345.83</v>
+      </c>
+      <c r="D685" t="n">
+        <v>359.98</v>
+      </c>
+      <c r="E685" t="n">
+        <v>366.55</v>
+      </c>
+      <c r="F685" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="G685" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>333.67</v>
+      </c>
+      <c r="C686" t="n">
+        <v>344.57</v>
+      </c>
+      <c r="D686" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="E686" t="n">
+        <v>364.63</v>
+      </c>
+      <c r="F686" t="n">
+        <v>361.58</v>
+      </c>
+      <c r="G686" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="H686" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20914,7 +21034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B726"/>
+  <dimension ref="A1:B731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28177,6 +28297,56 @@
       </c>
       <c r="B726" t="n">
         <v>-0.53</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -28345,28 +28515,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2825000637103376</v>
+        <v>0.2697643700116975</v>
       </c>
       <c r="J2" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K2" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05026962546094071</v>
+        <v>0.04622474030434343</v>
       </c>
       <c r="M2" t="n">
-        <v>7.520268769921071</v>
+        <v>7.533339365202852</v>
       </c>
       <c r="N2" t="n">
-        <v>82.37772540516973</v>
+        <v>82.59834648647504</v>
       </c>
       <c r="O2" t="n">
-        <v>9.076217571498038</v>
+        <v>9.088363245737652</v>
       </c>
       <c r="P2" t="n">
-        <v>337.878216464661</v>
+        <v>338.0181510248367</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28423,28 +28593,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.173869785751493</v>
+        <v>0.1646228858240193</v>
       </c>
       <c r="J3" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K3" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02272236765583546</v>
+        <v>0.02056660692853574</v>
       </c>
       <c r="M3" t="n">
-        <v>6.971489958229283</v>
+        <v>6.964869936166672</v>
       </c>
       <c r="N3" t="n">
-        <v>71.03798460089619</v>
+        <v>70.99426771769492</v>
       </c>
       <c r="O3" t="n">
-        <v>8.428403443173339</v>
+        <v>8.425809617935533</v>
       </c>
       <c r="P3" t="n">
-        <v>348.726913422631</v>
+        <v>348.8285135553914</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28501,28 +28671,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02785697433438552</v>
+        <v>0.02601525861940461</v>
       </c>
       <c r="J4" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K4" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006639913862550584</v>
+        <v>0.0005862504381914935</v>
       </c>
       <c r="M4" t="n">
-        <v>6.581193808422938</v>
+        <v>6.551606027939018</v>
       </c>
       <c r="N4" t="n">
-        <v>63.81091859462417</v>
+        <v>63.46715613215081</v>
       </c>
       <c r="O4" t="n">
-        <v>7.988173670785092</v>
+        <v>7.966627651155212</v>
       </c>
       <c r="P4" t="n">
-        <v>360.9511676823444</v>
+        <v>360.97142183285</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28579,28 +28749,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0762948042989868</v>
+        <v>-0.07600098976106952</v>
       </c>
       <c r="J5" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K5" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006620383807362962</v>
+        <v>0.006652249815337186</v>
       </c>
       <c r="M5" t="n">
-        <v>5.663234680655915</v>
+        <v>5.635161925756045</v>
       </c>
       <c r="N5" t="n">
-        <v>47.71995446778206</v>
+        <v>47.44624667236491</v>
       </c>
       <c r="O5" t="n">
-        <v>6.90796312003633</v>
+        <v>6.888123595897863</v>
       </c>
       <c r="P5" t="n">
-        <v>367.9479582400522</v>
+        <v>367.9447388702984</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28657,28 +28827,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.009460137592964862</v>
+        <v>-0.00937924881567738</v>
       </c>
       <c r="J6" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K6" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L6" t="n">
-        <v>9.361449608158434e-05</v>
+        <v>9.319043677891159e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>5.833767109952591</v>
+        <v>5.801858129153025</v>
       </c>
       <c r="N6" t="n">
-        <v>52.22628826653968</v>
+        <v>51.9224165232532</v>
       </c>
       <c r="O6" t="n">
-        <v>7.226775786375255</v>
+        <v>7.205721096687909</v>
       </c>
       <c r="P6" t="n">
-        <v>361.5297293998523</v>
+        <v>361.5288357436962</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28735,28 +28905,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06444167299629971</v>
+        <v>0.06770972207944918</v>
       </c>
       <c r="J7" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K7" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00439336472844809</v>
+        <v>0.004905045754210358</v>
       </c>
       <c r="M7" t="n">
-        <v>5.729606067629828</v>
+        <v>5.71179387605809</v>
       </c>
       <c r="N7" t="n">
-        <v>51.41645786805796</v>
+        <v>51.16277917814116</v>
       </c>
       <c r="O7" t="n">
-        <v>7.17052702861219</v>
+        <v>7.152816171141347</v>
       </c>
       <c r="P7" t="n">
-        <v>349.4030305125661</v>
+        <v>349.3671203732634</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28794,7 +28964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H682"/>
+  <dimension ref="A1:H686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57441,6 +57611,174 @@
         </is>
       </c>
     </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-37.18107232723575,175.88501573978746</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-37.18176888407356,175.88524360232174</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-37.18245681817237,175.8855359310211</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-37.18312955481429,175.88580793920292</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-37.18381493839223,175.88606209732976</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>-37.18449728868485,175.88634828080433</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-37.181072601393346,175.88501340085537</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-37.1817678527019,175.88525240123815</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-37.18245657899935,175.88553736355678</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-37.18312875147867,175.8858109269607</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-37.18381245288128,175.88606933909915</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-37.18449728868485,175.88634828080433</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-37.181072601393346,175.88501340085537</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-37.18176800936599,175.8852510646939</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-37.1824593570849,175.88552072410346</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-37.18312961219541,175.88580772579164</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-37.18381089055986,175.88607389106818</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-37.184495378857974,175.88635350220966</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-37.18107382857439,175.88500293134948</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-37.181769654338055,175.88523703097894</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-37.18246373578465,175.88549449767757</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-37.18313512078054,175.88578723830798</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-37.18381163621327,175.88607171853755</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-37.18449504182967,175.88635442363412</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
